--- a/Lista_de_marcas-modelo.xlsx
+++ b/Lista_de_marcas-modelo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://suramericana-my.sharepoint.com/personal/matias_valenzuela_ext_segurossura_cl/Documents/Documentos/Reportes quarto/Mas-robados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="146" documentId="13_ncr:1_{1EC2F46D-D03E-4914-A813-C0437C0D954D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B7E39C1-D85F-45D4-8421-32A6519917EF}"/>
+  <xr:revisionPtr revIDLastSave="175" documentId="13_ncr:1_{1EC2F46D-D03E-4914-A813-C0437C0D954D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EFBDB823-472E-4768-8DA8-28A253F95CAD}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="34">
   <si>
     <t>MARCA_MODELO</t>
   </si>
@@ -49,9 +49,6 @@
     <t>KIA MOTORS - SOLUTO</t>
   </si>
   <si>
-    <t>VOLKSWAGEN - AMAROK</t>
-  </si>
-  <si>
     <t>MAZDA - 3 SPORT</t>
   </si>
   <si>
@@ -70,28 +67,13 @@
     <t>NISSAN - VERSA</t>
   </si>
   <si>
-    <t>KIA MOTORS - SOUL</t>
-  </si>
-  <si>
-    <t>PEUGEOT - 301</t>
-  </si>
-  <si>
     <t>TOYOTA - LAND CRUISER</t>
   </si>
   <si>
     <t>KIA MOTORS - FRONTIER</t>
   </si>
   <si>
-    <t>PEUGEOT - 5008</t>
-  </si>
-  <si>
-    <t>MAHINDRA - XUV 500</t>
-  </si>
-  <si>
     <t>MITSUBISHI - L-200</t>
-  </si>
-  <si>
-    <t>HYUNDAI - H-1</t>
   </si>
   <si>
     <t>TOYOTA - HI-LUX</t>
@@ -555,7 +537,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:G31"/>
+  <dimension ref="B1:G25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="31.7265625" style="2" customWidth="1"/>
@@ -581,19 +563,19 @@
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.35">
@@ -601,10 +583,10 @@
         <v>1</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D3" s="4">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.35">
@@ -612,7 +594,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D4" s="4">
         <v>3.5</v>
@@ -623,7 +605,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.35">
@@ -631,7 +613,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D6" s="4">
         <v>1.6</v>
@@ -642,7 +624,7 @@
         <v>5</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D7" s="4">
         <v>1.8</v>
@@ -653,7 +635,7 @@
         <v>6</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D8" s="4">
         <v>0.7</v>
@@ -664,7 +646,7 @@
         <v>7</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D9" s="4">
         <v>0.8</v>
@@ -675,7 +657,7 @@
         <v>8</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D10" s="4">
         <v>2.6</v>
@@ -686,7 +668,10 @@
         <v>9</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>28</v>
+        <v>22</v>
+      </c>
+      <c r="D11" s="4">
+        <v>0.8</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.35">
@@ -694,10 +679,7 @@
         <v>10</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D12" s="4">
-        <v>0.8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.35">
@@ -705,7 +687,10 @@
         <v>11</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>28</v>
+        <v>22</v>
+      </c>
+      <c r="D13" s="4">
+        <v>0.6</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.35">
@@ -713,10 +698,10 @@
         <v>12</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D14" s="4">
-        <v>0.6</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.35">
@@ -724,10 +709,13 @@
         <v>13</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D15" s="4">
-        <v>3.7</v>
+        <v>1.2</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.35">
@@ -735,13 +723,10 @@
         <v>14</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D16" s="4">
-        <v>1.2</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>34</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.35">
@@ -749,10 +734,10 @@
         <v>15</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D17" s="4">
-        <v>1</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.35">
@@ -760,7 +745,10 @@
         <v>16</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>29</v>
+        <v>23</v>
+      </c>
+      <c r="D18" s="4">
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.35">
@@ -768,7 +756,13 @@
         <v>17</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>28</v>
+        <v>23</v>
+      </c>
+      <c r="D19" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.35">
@@ -776,127 +770,67 @@
         <v>18</v>
       </c>
       <c r="C20" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" s="4">
+        <v>1.8</v>
+      </c>
+      <c r="E20" s="4" t="s">
         <v>29</v>
-      </c>
-      <c r="D20" s="4">
-        <v>7.3</v>
       </c>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B21" s="4" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D21" s="4">
-        <v>4</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B22" s="4" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>28</v>
+        <v>22</v>
+      </c>
+      <c r="D22" s="4">
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B23" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>28</v>
+        <v>22</v>
+      </c>
+      <c r="D23" s="4">
+        <v>2.4</v>
       </c>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B24" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D24" s="4">
-        <v>1.5</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>35</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B25" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B26" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D26" s="4">
-        <v>1.8</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B27" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D27" s="4">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B28" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D28" s="4">
-        <v>2.2000000000000002</v>
-      </c>
-    </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B29" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D29" s="4">
-        <v>2.4</v>
-      </c>
-    </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B30" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D30" s="4">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B31" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D31" s="4">
+      <c r="D25" s="4">
         <v>4.4000000000000004</v>
       </c>
     </row>
